--- a/VerveStacks_POL_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8635F15-8E03-4920-8273-A5C4A897B28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3586FB60-C414-4EFB-B153-8CB0318A4146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="364">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -1091,48 +1091,12 @@
     <t>grid node -- way/133537926-220</t>
   </si>
   <si>
-    <t>e_w139452056-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/139452056-400</t>
-  </si>
-  <si>
-    <t>e_w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/166838338-400</t>
-  </si>
-  <si>
-    <t>e_w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/173613665-220</t>
-  </si>
-  <si>
-    <t>e_w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/183945016-220</t>
-  </si>
-  <si>
     <t>e_w191035265-220_POL</t>
   </si>
   <si>
     <t>grid node -- way/191035265-220</t>
   </si>
   <si>
-    <t>e_w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/215282393-400</t>
-  </si>
-  <si>
-    <t>e_w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/255277953-400</t>
-  </si>
-  <si>
     <t>e_w255314292_POL</t>
   </si>
   <si>
@@ -1161,12 +1125,6 @@
   </si>
   <si>
     <t>grid node -- way/39428977-400</t>
-  </si>
-  <si>
-    <t>e_w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>grid node -- way/44389929-220</t>
   </si>
   <si>
     <t>e_w86494356-400_POL</t>
@@ -5450,8 +5408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D22017-EFB2-43EC-A837-98E3B2600621}">
-  <dimension ref="B3:I22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A28F2F6E-CB52-45A8-B69E-41B3462B28EA}">
+  <dimension ref="B3:I15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="3" spans="2:9">
@@ -5768,188 +5726,6 @@
         <v>343</v>
       </c>
       <c r="I15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>364</v>
-      </c>
-      <c r="D16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" t="s">
-        <v>365</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>343</v>
-      </c>
-      <c r="I16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>366</v>
-      </c>
-      <c r="D17" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" t="s">
-        <v>367</v>
-      </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>343</v>
-      </c>
-      <c r="I17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>368</v>
-      </c>
-      <c r="D18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E18" t="s">
-        <v>369</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>343</v>
-      </c>
-      <c r="I18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>370</v>
-      </c>
-      <c r="D19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" t="s">
-        <v>371</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>343</v>
-      </c>
-      <c r="I19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>372</v>
-      </c>
-      <c r="D20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E20" t="s">
-        <v>373</v>
-      </c>
-      <c r="F20" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" t="s">
-        <v>343</v>
-      </c>
-      <c r="I20" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>374</v>
-      </c>
-      <c r="D21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E21" t="s">
-        <v>375</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>343</v>
-      </c>
-      <c r="I21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>376</v>
-      </c>
-      <c r="D22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E22" t="s">
-        <v>377</v>
-      </c>
-      <c r="F22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" t="s">
-        <v>343</v>
-      </c>
-      <c r="I22" t="s">
         <v>241</v>
       </c>
     </row>
